--- a/Result/profitability/8074.xlsx
+++ b/Result/profitability/8074.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3174999999999999</v>
+        <v>0.3337499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>22.0125</v>
+        <v>22.41625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.3249999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.9675</v>
+        <v>21.4625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3075</v>
+        <v>0.3312499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>19.73</v>
+        <v>20.4025</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2612499999999999</v>
+        <v>0.3024999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>18.9625</v>
+        <v>19.80125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="N6" t="n">
-        <v>18.59375</v>
+        <v>19.1025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26</v>
+        <v>0.2462499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>19.0075</v>
+        <v>19.095</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.275</v>
+        <v>0.26375</v>
       </c>
       <c r="N8" t="n">
-        <v>18.84375</v>
+        <v>18.94625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>0.30625</v>
+        <v>0.3062499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>19.44375</v>
@@ -1772,7 +1772,7 @@
         <v>0.37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3274999999999999</v>
+        <v>0.3275</v>
       </c>
       <c r="N11" t="n">
         <v>19.69125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>420</v>
+      </c>
+      <c r="D75" t="n">
+        <v>306</v>
+      </c>
+      <c r="E75" t="n">
+        <v>114</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.99125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1730769230769231</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03120243531202438</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.710000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3290828837665523</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
